--- a/RBLX.xlsx
+++ b/RBLX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA353EC-61CC-47D9-8041-172E650790E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90ADE289-C2DD-4617-ADC7-0F1D0CBC418E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-42540" yWindow="2190" windowWidth="40710" windowHeight="17760" activeTab="1" xr2:uid="{6D0C9AA7-E60A-45CC-9230-29CA233AF480}"/>
+    <workbookView xWindow="21590" yWindow="3530" windowWidth="16490" windowHeight="16350" xr2:uid="{6D0C9AA7-E60A-45CC-9230-29CA233AF480}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="90">
   <si>
     <t>Price</t>
   </si>
@@ -295,6 +295,18 @@
   </si>
   <si>
     <t>Gross Margin</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -344,7 +356,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -370,7 +382,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -627,6 +638,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -634,7 +646,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1229,13 +1240,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>43</xdr:col>
+      <xdr:col>45</xdr:col>
       <xdr:colOff>43552</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>10422</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>43</xdr:col>
+      <xdr:col>45</xdr:col>
       <xdr:colOff>43552</xdr:colOff>
       <xdr:row>64</xdr:row>
       <xdr:rowOff>28281</xdr:rowOff>
@@ -1279,16 +1290,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>39976</xdr:colOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>26839</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>21648</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>39976</xdr:colOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>26839</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>143886</xdr:rowOff>
+      <xdr:rowOff>122238</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1303,8 +1314,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17141681" y="21648"/>
-          <a:ext cx="0" cy="10855181"/>
+          <a:off x="19641770" y="0"/>
+          <a:ext cx="0" cy="10693893"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1329,16 +1340,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>186171</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>116898</xdr:rowOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>102964</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>103760</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>285752</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>73602</xdr:rowOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>202545</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>60464</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1675,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>84</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="11:13" x14ac:dyDescent="0.25">
@@ -1683,11 +1694,10 @@
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <f>553.798118+51.337302</f>
-        <v>605.13542000000007</v>
+        <v>712</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="11:13" x14ac:dyDescent="0.25">
@@ -1696,7 +1706,7 @@
       </c>
       <c r="L4" s="2">
         <f>+L2*L3</f>
-        <v>50831.375280000007</v>
+        <v>32752</v>
       </c>
       <c r="M4" s="4"/>
     </row>
@@ -1705,11 +1715,11 @@
         <v>3</v>
       </c>
       <c r="L5" s="2">
-        <f>966.406+1445.689+1189.135</f>
-        <v>3601.2300000000005</v>
+        <f>+Model!AE37</f>
+        <v>6165</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="11:13" x14ac:dyDescent="0.25">
@@ -1717,10 +1727,11 @@
         <v>4</v>
       </c>
       <c r="L6" s="2">
-        <v>1005.679</v>
+        <f>+Model!AE52</f>
+        <v>1008</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="11:13" x14ac:dyDescent="0.25">
@@ -1729,7 +1740,7 @@
       </c>
       <c r="L7" s="2">
         <f>L4-L5+L6</f>
-        <v>48235.824280000001</v>
+        <v>27595</v>
       </c>
     </row>
     <row r="11" spans="11:13" x14ac:dyDescent="0.25">
@@ -1752,7 +1763,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDC7D717-BF13-4B06-BD00-B0629B64921F}">
-  <dimension ref="A1:BB68"/>
+  <dimension ref="A1:BD68"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -1760,12 +1771,12 @@
     <col min="3" max="21" width="9.1796875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:56" x14ac:dyDescent="0.25">
       <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
@@ -1850,83 +1861,95 @@
       <c r="AD2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="AH2">
+      <c r="AE2" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF2" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG2" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AH2" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ2">
         <v>2015</v>
       </c>
-      <c r="AI2">
-        <f>+AH2+1</f>
+      <c r="AK2">
+        <f>+AJ2+1</f>
         <v>2016</v>
       </c>
-      <c r="AJ2">
-        <f t="shared" ref="AJ2:AT2" si="0">+AI2+1</f>
+      <c r="AL2">
+        <f t="shared" ref="AL2:AV2" si="0">+AK2+1</f>
         <v>2017</v>
       </c>
-      <c r="AK2">
+      <c r="AM2">
         <f t="shared" si="0"/>
         <v>2018</v>
       </c>
-      <c r="AL2">
+      <c r="AN2">
         <f t="shared" si="0"/>
         <v>2019</v>
       </c>
-      <c r="AM2">
+      <c r="AO2">
         <f t="shared" si="0"/>
         <v>2020</v>
       </c>
-      <c r="AN2">
+      <c r="AP2">
         <f t="shared" si="0"/>
         <v>2021</v>
       </c>
-      <c r="AO2">
+      <c r="AQ2">
         <f t="shared" si="0"/>
         <v>2022</v>
       </c>
-      <c r="AP2">
+      <c r="AR2">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="AQ2">
+      <c r="AS2">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="AR2">
+      <c r="AT2">
         <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="AS2">
+      <c r="AU2">
         <f t="shared" si="0"/>
         <v>2026</v>
       </c>
-      <c r="AT2">
+      <c r="AV2">
         <f t="shared" si="0"/>
         <v>2027</v>
       </c>
-      <c r="AU2">
+      <c r="AW2">
         <v>2028</v>
       </c>
-      <c r="AV2">
+      <c r="AX2">
         <v>2029</v>
       </c>
-      <c r="AW2">
+      <c r="AY2">
         <v>2030</v>
       </c>
-      <c r="AX2">
+      <c r="AZ2">
         <v>2031</v>
       </c>
-      <c r="AY2">
+      <c r="BA2">
         <v>2032</v>
       </c>
-      <c r="AZ2">
+      <c r="BB2">
         <v>2033</v>
       </c>
-      <c r="BA2">
+      <c r="BC2">
         <v>2034</v>
       </c>
-      <c r="BB2">
+      <c r="BD2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:56" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>9</v>
       </c>
@@ -2005,20 +2028,20 @@
       <c r="AA3">
         <v>97.8</v>
       </c>
-      <c r="AM3">
+      <c r="AO3">
         <f>J3</f>
         <v>37.1</v>
       </c>
-      <c r="AN3">
+      <c r="AP3">
         <f>N3</f>
         <v>49.5</v>
       </c>
-      <c r="AO3">
+      <c r="AQ3">
         <f>R3</f>
         <v>58.8</v>
       </c>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:56" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>84</v>
       </c>
@@ -2047,7 +2070,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="5" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:56" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
@@ -2127,7 +2150,7 @@
         <v>21700</v>
       </c>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:56" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>28</v>
       </c>
@@ -2235,7 +2258,7 @@
       <c r="AC6" s="7"/>
       <c r="AD6" s="7"/>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:56" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>29</v>
       </c>
@@ -2291,7 +2314,7 @@
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
     </row>
-    <row r="8" spans="1:54" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:56" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>30</v>
       </c>
@@ -2346,34 +2369,34 @@
       <c r="AA8" s="2">
         <v>1206.7</v>
       </c>
-      <c r="AM8" s="2">
+      <c r="AO8" s="2">
         <v>1882.5429999999999</v>
       </c>
-      <c r="AN8" s="2">
+      <c r="AP8" s="2">
         <v>2725.7060000000001</v>
       </c>
-      <c r="AO8" s="2">
+      <c r="AQ8" s="2">
         <v>2872.2579999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:56" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>49</v>
       </c>
-      <c r="AM9" s="2"/>
-      <c r="AN9" s="2">
+      <c r="AO9" s="2"/>
+      <c r="AP9" s="2">
         <v>678</v>
       </c>
-      <c r="AO9" s="2">
+      <c r="AQ9" s="2">
         <v>725</v>
       </c>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="AM10" s="2"/>
-      <c r="AN10" s="2"/>
-      <c r="AO10" s="10"/>
-    </row>
-    <row r="12" spans="1:54" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AO10" s="2"/>
+      <c r="AP10" s="2"/>
+      <c r="AQ10" s="10"/>
+    </row>
+    <row r="12" spans="1:56" s="9" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B12" s="9" t="s">
         <v>31</v>
       </c>
@@ -2431,80 +2454,80 @@
         <v>1035.2070000000001</v>
       </c>
       <c r="AB12" s="9">
-        <f>+W12*1.3</f>
-        <v>1041.69</v>
+        <v>1080.6769999999999</v>
       </c>
       <c r="AC12" s="9">
-        <f>+X12*1.25</f>
-        <v>1116.92875</v>
+        <v>1359.646</v>
       </c>
       <c r="AD12" s="9">
-        <f>+Y12*1.25</f>
-        <v>1148.6912499999999</v>
-      </c>
-      <c r="AM12" s="9">
+        <v>1415.021</v>
+      </c>
+      <c r="AE12" s="9">
+        <v>1442</v>
+      </c>
+      <c r="AO12" s="9">
         <v>923.88499999999999</v>
       </c>
-      <c r="AN12" s="9">
+      <c r="AP12" s="9">
         <v>1919.181</v>
       </c>
-      <c r="AO12" s="9">
+      <c r="AQ12" s="9">
         <v>2225.0520000000001</v>
       </c>
-      <c r="AP12" s="9">
+      <c r="AR12" s="9">
         <f>SUM(S12:V12)</f>
         <v>2799.308</v>
       </c>
-      <c r="AQ12" s="9">
+      <c r="AS12" s="9">
         <f>SUM(W12:Z12)</f>
         <v>3601.9789999999998</v>
       </c>
-      <c r="AR12" s="9">
+      <c r="AT12" s="9">
         <f>SUM(AA12:AD12)</f>
-        <v>4342.5169999999998</v>
-      </c>
-      <c r="AS12" s="9">
-        <f>+AR12*1.25</f>
-        <v>5428.1462499999998</v>
-      </c>
-      <c r="AT12" s="9">
-        <f>+AS12*1.25</f>
-        <v>6785.1828124999993</v>
+        <v>4890.5509999999995</v>
       </c>
       <c r="AU12" s="9">
         <f>+AT12*1.25</f>
-        <v>8481.478515625</v>
+        <v>6113.1887499999993</v>
       </c>
       <c r="AV12" s="9">
         <f>+AU12*1.25</f>
-        <v>10601.84814453125</v>
+        <v>7641.4859374999996</v>
       </c>
       <c r="AW12" s="9">
-        <f>+AV12*1.2</f>
-        <v>12722.2177734375</v>
+        <f>+AV12*1.25</f>
+        <v>9551.857421875</v>
       </c>
       <c r="AX12" s="9">
-        <f t="shared" ref="AV12:BB12" si="2">+AW12*1.1</f>
-        <v>13994.439550781251</v>
+        <f>+AW12*1.25</f>
+        <v>11939.82177734375</v>
       </c>
       <c r="AY12" s="9">
-        <f t="shared" si="2"/>
-        <v>15393.883505859378</v>
+        <f>+AX12*1.2</f>
+        <v>14327.7861328125</v>
       </c>
       <c r="AZ12" s="9">
-        <f t="shared" si="2"/>
-        <v>16933.271856445317</v>
+        <f t="shared" ref="AZ12:BD12" si="2">+AY12*1.1</f>
+        <v>15760.564746093751</v>
       </c>
       <c r="BA12" s="9">
         <f t="shared" si="2"/>
-        <v>18626.599042089849</v>
+        <v>17336.621220703128</v>
       </c>
       <c r="BB12" s="9">
         <f t="shared" si="2"/>
-        <v>20489.258946298836</v>
-      </c>
-    </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
+        <v>19070.28334277344</v>
+      </c>
+      <c r="BC12" s="9">
+        <f t="shared" si="2"/>
+        <v>20977.311677050788</v>
+      </c>
+      <c r="BD12" s="9">
+        <f t="shared" si="2"/>
+        <v>23075.04284475587</v>
+      </c>
+    </row>
+    <row r="13" spans="1:56" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>35</v>
       </c>
@@ -2547,26 +2570,38 @@
       <c r="Z13" s="2">
         <v>218.74100000000001</v>
       </c>
-      <c r="AA13" s="13">
+      <c r="AA13" s="2">
         <v>224.72499999999999</v>
       </c>
-      <c r="AM13" s="2"/>
-      <c r="AN13" s="2">
+      <c r="AB13" s="2">
+        <v>236.113</v>
+      </c>
+      <c r="AC13" s="2">
+        <v>296.45600000000002</v>
+      </c>
+      <c r="AD13" s="2">
+        <v>315.005</v>
+      </c>
+      <c r="AE13" s="2">
+        <v>294</v>
+      </c>
+      <c r="AO13" s="2"/>
+      <c r="AP13" s="2">
         <v>496.87</v>
       </c>
-      <c r="AO13" s="2">
+      <c r="AQ13" s="2">
         <v>547.65800000000002</v>
       </c>
-      <c r="AP13" s="13">
+      <c r="AR13" s="2">
         <f>SUM(S13:V13)</f>
         <v>649.11500000000001</v>
       </c>
-      <c r="AQ13" s="13">
+      <c r="AS13" s="2">
         <f>SUM(W13:Z13)</f>
         <v>801.16200000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:56" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>36</v>
       </c>
@@ -2609,26 +2644,38 @@
       <c r="Z14" s="2">
         <v>280.61</v>
       </c>
-      <c r="AA14" s="13">
+      <c r="AA14" s="2">
         <v>281.56400000000002</v>
       </c>
-      <c r="AM14" s="2"/>
-      <c r="AN14" s="2">
+      <c r="AB14" s="2">
+        <v>316.37099999999998</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>427.93099999999998</v>
+      </c>
+      <c r="AD14" s="2">
+        <v>477.24</v>
+      </c>
+      <c r="AE14" s="2">
+        <v>423</v>
+      </c>
+      <c r="AO14" s="2"/>
+      <c r="AP14" s="2">
         <v>538.32100000000003</v>
       </c>
-      <c r="AO14" s="2">
+      <c r="AQ14" s="2">
         <v>623.85500000000002</v>
       </c>
-      <c r="AP14" s="13">
-        <f t="shared" ref="AP14:AP15" si="3">SUM(S14:V14)</f>
+      <c r="AR14" s="2">
+        <f t="shared" ref="AR14:AR15" si="3">SUM(S14:V14)</f>
         <v>740.75199999999995</v>
       </c>
-      <c r="AQ14" s="13">
-        <f t="shared" ref="AQ14:AQ15" si="4">SUM(W14:Z14)</f>
+      <c r="AS14" s="2">
+        <f t="shared" ref="AS14:AS15" si="4">SUM(W14:Z14)</f>
         <v>922.82100000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:56" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>37</v>
       </c>
@@ -2671,26 +2718,38 @@
       <c r="Z15" s="2">
         <v>222.822</v>
       </c>
-      <c r="AA15" s="13">
+      <c r="AA15" s="2">
         <v>242.12700000000001</v>
       </c>
-      <c r="AM15" s="2"/>
-      <c r="AN15" s="2">
+      <c r="AB15" s="2">
+        <v>260.68400000000003</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>321.36500000000001</v>
+      </c>
+      <c r="AD15" s="2">
+        <v>329.27800000000002</v>
+      </c>
+      <c r="AE15" s="2">
+        <v>324</v>
+      </c>
+      <c r="AO15" s="2"/>
+      <c r="AP15" s="2">
         <v>533.20699999999999</v>
       </c>
-      <c r="AO15" s="2">
+      <c r="AQ15" s="2">
         <v>689.08100000000002</v>
       </c>
-      <c r="AP15" s="13">
+      <c r="AR15" s="2">
         <f t="shared" si="3"/>
         <v>878.36099999999988</v>
       </c>
-      <c r="AQ15" s="13">
+      <c r="AS15" s="2">
         <f t="shared" si="4"/>
         <v>915.41800000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:56" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>34</v>
       </c>
@@ -2751,80 +2810,84 @@
         <v>748.41600000000005</v>
       </c>
       <c r="AB16" s="7">
-        <f t="shared" ref="AB16:AD16" si="10">AB15+AB14+AB13</f>
-        <v>0</v>
+        <f t="shared" ref="AB16:AE16" si="10">AB15+AB14+AB13</f>
+        <v>813.16800000000012</v>
       </c>
       <c r="AC16" s="7">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1045.752</v>
       </c>
       <c r="AD16" s="7">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AM16" s="2"/>
-      <c r="AN16" s="2">
-        <f>+AN13+AN14+AN15</f>
+        <v>1121.5230000000001</v>
+      </c>
+      <c r="AE16" s="7">
+        <f t="shared" si="10"/>
+        <v>1041</v>
+      </c>
+      <c r="AO16" s="2"/>
+      <c r="AP16" s="2">
+        <f>+AP13+AP14+AP15</f>
         <v>1568.3980000000001</v>
       </c>
-      <c r="AO16" s="2">
-        <f>+AO13+AO14+AO15</f>
+      <c r="AQ16" s="2">
+        <f>+AQ13+AQ14+AQ15</f>
         <v>1860.5940000000001</v>
       </c>
-      <c r="AP16" s="2">
-        <f t="shared" ref="AP16:AQ16" si="11">+AP13+AP14+AP15</f>
+      <c r="AR16" s="2">
+        <f t="shared" ref="AR16:AS16" si="11">+AR13+AR14+AR15</f>
         <v>2268.2280000000001</v>
       </c>
-      <c r="AQ16" s="2">
+      <c r="AS16" s="2">
         <f t="shared" si="11"/>
         <v>2639.4010000000003</v>
       </c>
-      <c r="AR16" s="2">
-        <f>+AR12-AR17</f>
-        <v>2822.6360500000001</v>
-      </c>
-      <c r="AS16" s="2">
-        <f>+AS12-AS17</f>
-        <v>3256.8877499999999</v>
-      </c>
       <c r="AT16" s="2">
-        <f t="shared" ref="AS16:BB16" si="12">+AT12-AT17</f>
-        <v>3731.8505468749995</v>
+        <f>+AT12-AT17</f>
+        <v>3178.85815</v>
       </c>
       <c r="AU16" s="2">
-        <f t="shared" si="12"/>
-        <v>4240.7392578125</v>
+        <f>+AU12-AU17</f>
+        <v>3667.9132499999996</v>
       </c>
       <c r="AV16" s="2">
-        <f t="shared" si="12"/>
-        <v>4770.8316650390616</v>
+        <f t="shared" ref="AV16:BD16" si="12">+AV12-AV17</f>
+        <v>4202.8172656249999</v>
       </c>
       <c r="AW16" s="2">
         <f t="shared" si="12"/>
-        <v>5470.5536425781256</v>
+        <v>4775.9287109375</v>
       </c>
       <c r="AX16" s="2">
         <f t="shared" si="12"/>
-        <v>5597.7758203125013</v>
+        <v>5372.9197998046866</v>
       </c>
       <c r="AY16" s="2">
         <f t="shared" si="12"/>
-        <v>6157.5534023437522</v>
+        <v>6160.9480371093759</v>
       </c>
       <c r="AZ16" s="2">
         <f t="shared" si="12"/>
-        <v>6773.3087425781268</v>
+        <v>6304.2258984375003</v>
       </c>
       <c r="BA16" s="2">
         <f t="shared" si="12"/>
-        <v>7450.6396168359406</v>
+        <v>6934.648488281251</v>
       </c>
       <c r="BB16" s="2">
         <f t="shared" si="12"/>
-        <v>8195.7035785195349</v>
-      </c>
-    </row>
-    <row r="17" spans="2:54" x14ac:dyDescent="0.25">
+        <v>7628.1133371093765</v>
+      </c>
+      <c r="BC16" s="2">
+        <f t="shared" si="12"/>
+        <v>8390.9246708203154</v>
+      </c>
+      <c r="BD16" s="2">
+        <f t="shared" si="12"/>
+        <v>9230.0171379023486</v>
+      </c>
+    </row>
+    <row r="17" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>33</v>
       </c>
@@ -2885,80 +2948,84 @@
         <v>286.79100000000005</v>
       </c>
       <c r="AB17" s="7">
-        <f t="shared" ref="AB17:AD17" si="17">AB12-AB16</f>
-        <v>1041.69</v>
+        <f t="shared" ref="AB17:AE17" si="17">AB12-AB16</f>
+        <v>267.50899999999979</v>
       </c>
       <c r="AC17" s="7">
         <f t="shared" si="17"/>
-        <v>1116.92875</v>
+        <v>313.89400000000001</v>
       </c>
       <c r="AD17" s="7">
         <f t="shared" si="17"/>
-        <v>1148.6912499999999</v>
-      </c>
-      <c r="AM17" s="2"/>
-      <c r="AN17" s="2">
-        <f>+AN12-AN16</f>
+        <v>293.49799999999982</v>
+      </c>
+      <c r="AE17" s="7">
+        <f t="shared" si="17"/>
+        <v>401</v>
+      </c>
+      <c r="AO17" s="2"/>
+      <c r="AP17" s="2">
+        <f>+AP12-AP16</f>
         <v>350.7829999999999</v>
       </c>
-      <c r="AO17" s="2">
-        <f>+AO12-AO16</f>
+      <c r="AQ17" s="2">
+        <f>+AQ12-AQ16</f>
         <v>364.45800000000008</v>
       </c>
-      <c r="AP17" s="2">
-        <f t="shared" ref="AP17:AQ17" si="18">+AP12-AP16</f>
+      <c r="AR17" s="2">
+        <f t="shared" ref="AR17:AS17" si="18">+AR12-AR16</f>
         <v>531.07999999999993</v>
       </c>
-      <c r="AQ17" s="2">
+      <c r="AS17" s="2">
         <f t="shared" si="18"/>
         <v>962.57799999999952</v>
       </c>
-      <c r="AR17" s="2">
-        <f>+AR12*0.35</f>
-        <v>1519.8809499999998</v>
-      </c>
-      <c r="AS17" s="2">
-        <f>+AS12*0.4</f>
-        <v>2171.2584999999999</v>
-      </c>
       <c r="AT17" s="2">
-        <f>+AT12*0.45</f>
-        <v>3053.3322656249998</v>
+        <f>+AT12*0.35</f>
+        <v>1711.6928499999997</v>
       </c>
       <c r="AU17" s="2">
-        <f>+AU12*0.5</f>
-        <v>4240.7392578125</v>
+        <f>+AU12*0.4</f>
+        <v>2445.2754999999997</v>
       </c>
       <c r="AV17" s="2">
-        <f>+AV12*0.55</f>
-        <v>5831.0164794921884</v>
+        <f>+AV12*0.45</f>
+        <v>3438.6686718749997</v>
       </c>
       <c r="AW17" s="2">
-        <f>+AW12*0.57</f>
-        <v>7251.6641308593744</v>
+        <f>+AW12*0.5</f>
+        <v>4775.9287109375</v>
       </c>
       <c r="AX17" s="2">
-        <f>+AX12*0.6</f>
-        <v>8396.6637304687501</v>
+        <f>+AX12*0.55</f>
+        <v>6566.9019775390634</v>
       </c>
       <c r="AY17" s="2">
-        <f t="shared" ref="AY17:BB17" si="19">+AY12*0.6</f>
-        <v>9236.3301035156255</v>
+        <f>+AY12*0.57</f>
+        <v>8166.8380957031241</v>
       </c>
       <c r="AZ17" s="2">
-        <f t="shared" si="19"/>
-        <v>10159.96311386719</v>
+        <f>+AZ12*0.6</f>
+        <v>9456.3388476562504</v>
       </c>
       <c r="BA17" s="2">
-        <f t="shared" si="19"/>
-        <v>11175.959425253908</v>
+        <f t="shared" ref="BA17:BD17" si="19">+BA12*0.6</f>
+        <v>10401.972732421877</v>
       </c>
       <c r="BB17" s="2">
         <f t="shared" si="19"/>
-        <v>12293.555367779301</v>
-      </c>
-    </row>
-    <row r="18" spans="2:54" x14ac:dyDescent="0.25">
+        <v>11442.170005664064</v>
+      </c>
+      <c r="BC17" s="2">
+        <f t="shared" si="19"/>
+        <v>12586.387006230472</v>
+      </c>
+      <c r="BD17" s="2">
+        <f t="shared" si="19"/>
+        <v>13845.025706853521</v>
+      </c>
+    </row>
+    <row r="18" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>38</v>
       </c>
@@ -3001,70 +3068,82 @@
       <c r="Z18" s="2">
         <v>355.03399999999999</v>
       </c>
-      <c r="AA18" s="13">
+      <c r="AA18" s="2">
         <v>374.6</v>
       </c>
-      <c r="AM18" s="2"/>
-      <c r="AN18" s="2">
+      <c r="AB18" s="2">
+        <v>384.99599999999998</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>398.30599999999998</v>
+      </c>
+      <c r="AD18" s="2">
+        <v>409.84500000000003</v>
+      </c>
+      <c r="AE18" s="2">
+        <v>422</v>
+      </c>
+      <c r="AO18" s="2"/>
+      <c r="AP18" s="2">
         <v>533.20699999999999</v>
       </c>
-      <c r="AO18" s="2">
+      <c r="AQ18" s="2">
         <v>873.47699999999998</v>
       </c>
-      <c r="AP18" s="13">
-        <f t="shared" ref="AP18:AP20" si="20">SUM(S18:V18)</f>
+      <c r="AR18" s="2">
+        <f t="shared" ref="AR18:AR20" si="20">SUM(S18:V18)</f>
         <v>1253.598</v>
       </c>
-      <c r="AQ18" s="13">
-        <f t="shared" ref="AQ18:AQ20" si="21">SUM(W18:Z18)</f>
+      <c r="AS18" s="2">
+        <f t="shared" ref="AS18:AS20" si="21">SUM(W18:Z18)</f>
         <v>1444.2069999999999</v>
       </c>
-      <c r="AR18" s="2">
-        <f t="shared" ref="AR18:BB18" si="22">+AQ18*1.05</f>
+      <c r="AT18" s="2">
+        <f t="shared" ref="AT18:BD18" si="22">+AS18*1.05</f>
         <v>1516.4173499999999</v>
       </c>
-      <c r="AS18" s="2">
+      <c r="AU18" s="2">
         <f t="shared" si="22"/>
         <v>1592.2382175</v>
       </c>
-      <c r="AT18" s="2">
+      <c r="AV18" s="2">
         <f t="shared" si="22"/>
         <v>1671.8501283750002</v>
       </c>
-      <c r="AU18" s="2">
+      <c r="AW18" s="2">
         <f t="shared" si="22"/>
         <v>1755.4426347937504</v>
       </c>
-      <c r="AV18" s="2">
+      <c r="AX18" s="2">
         <f t="shared" si="22"/>
         <v>1843.214766533438</v>
       </c>
-      <c r="AW18" s="2">
+      <c r="AY18" s="2">
         <f t="shared" si="22"/>
         <v>1935.3755048601099</v>
       </c>
-      <c r="AX18" s="2">
+      <c r="AZ18" s="2">
         <f t="shared" si="22"/>
         <v>2032.1442801031155</v>
       </c>
-      <c r="AY18" s="2">
+      <c r="BA18" s="2">
         <f t="shared" si="22"/>
         <v>2133.7514941082713</v>
       </c>
-      <c r="AZ18" s="2">
+      <c r="BB18" s="2">
         <f t="shared" si="22"/>
         <v>2240.439068813685</v>
       </c>
-      <c r="BA18" s="2">
+      <c r="BC18" s="2">
         <f t="shared" si="22"/>
         <v>2352.4610222543693</v>
       </c>
-      <c r="BB18" s="2">
+      <c r="BD18" s="2">
         <f t="shared" si="22"/>
         <v>2470.084073367088</v>
       </c>
     </row>
-    <row r="19" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>39</v>
       </c>
@@ -3107,70 +3186,82 @@
       <c r="Z19" s="2">
         <v>105.32299999999999</v>
       </c>
-      <c r="AA19" s="13">
+      <c r="AA19" s="2">
         <v>119.13200000000001</v>
       </c>
-      <c r="AM19" s="2"/>
-      <c r="AN19" s="2">
+      <c r="AB19" s="2">
+        <v>152.166</v>
+      </c>
+      <c r="AC19" s="2">
+        <v>144.99</v>
+      </c>
+      <c r="AD19" s="2">
+        <v>163.82599999999999</v>
+      </c>
+      <c r="AE19" s="2">
+        <v>209</v>
+      </c>
+      <c r="AO19" s="2"/>
+      <c r="AP19" s="2">
         <v>303.02</v>
       </c>
-      <c r="AO19" s="2">
+      <c r="AQ19" s="2">
         <v>297.31700000000001</v>
       </c>
-      <c r="AP19" s="13">
+      <c r="AR19" s="2">
         <f t="shared" si="20"/>
         <v>390.05500000000001</v>
       </c>
-      <c r="AQ19" s="13">
+      <c r="AS19" s="2">
         <f t="shared" si="21"/>
         <v>407.50699999999995</v>
       </c>
-      <c r="AR19" s="2">
-        <f t="shared" ref="AR19:BB19" si="23">+AQ19*1.05</f>
+      <c r="AT19" s="2">
+        <f t="shared" ref="AT19:BD19" si="23">+AS19*1.05</f>
         <v>427.88234999999997</v>
       </c>
-      <c r="AS19" s="2">
+      <c r="AU19" s="2">
         <f t="shared" si="23"/>
         <v>449.27646749999997</v>
       </c>
-      <c r="AT19" s="2">
+      <c r="AV19" s="2">
         <f t="shared" si="23"/>
         <v>471.74029087499997</v>
       </c>
-      <c r="AU19" s="2">
+      <c r="AW19" s="2">
         <f t="shared" si="23"/>
         <v>495.32730541874997</v>
       </c>
-      <c r="AV19" s="2">
+      <c r="AX19" s="2">
         <f t="shared" si="23"/>
         <v>520.09367068968754</v>
       </c>
-      <c r="AW19" s="2">
+      <c r="AY19" s="2">
         <f t="shared" si="23"/>
         <v>546.098354224172</v>
       </c>
-      <c r="AX19" s="2">
+      <c r="AZ19" s="2">
         <f t="shared" si="23"/>
         <v>573.40327193538064</v>
       </c>
-      <c r="AY19" s="2">
+      <c r="BA19" s="2">
         <f t="shared" si="23"/>
         <v>602.07343553214969</v>
       </c>
-      <c r="AZ19" s="2">
+      <c r="BB19" s="2">
         <f t="shared" si="23"/>
         <v>632.17710730875717</v>
       </c>
-      <c r="BA19" s="2">
+      <c r="BC19" s="2">
         <f t="shared" si="23"/>
         <v>663.78596267419505</v>
       </c>
-      <c r="BB19" s="2">
+      <c r="BD19" s="2">
         <f t="shared" si="23"/>
         <v>696.97526080790487</v>
       </c>
     </row>
-    <row r="20" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>40</v>
       </c>
@@ -3213,70 +3304,82 @@
       <c r="Z20" s="2">
         <v>49.765000000000001</v>
       </c>
-      <c r="AA20" s="13">
+      <c r="AA20" s="2">
         <v>47.768000000000001</v>
       </c>
-      <c r="AM20" s="2"/>
-      <c r="AN20" s="2">
+      <c r="AB20" s="2">
+        <v>52.807000000000002</v>
+      </c>
+      <c r="AC20" s="2">
+        <v>67.132999999999996</v>
+      </c>
+      <c r="AD20" s="2">
+        <v>78.465000000000003</v>
+      </c>
+      <c r="AE20" s="2">
+        <v>64</v>
+      </c>
+      <c r="AO20" s="2"/>
+      <c r="AP20" s="2">
         <v>86.363</v>
       </c>
-      <c r="AO20" s="2">
+      <c r="AQ20" s="2">
         <v>117.44799999999999</v>
       </c>
-      <c r="AP20" s="13">
+      <c r="AR20" s="2">
         <f t="shared" si="20"/>
         <v>146.45999999999998</v>
       </c>
-      <c r="AQ20" s="13">
+      <c r="AS20" s="2">
         <f t="shared" si="21"/>
         <v>174.18099999999998</v>
       </c>
-      <c r="AR20" s="2">
-        <f>+AQ20*1.05</f>
+      <c r="AT20" s="2">
+        <f>+AS20*1.05</f>
         <v>182.89005</v>
       </c>
-      <c r="AS20" s="2">
-        <f t="shared" ref="AS20:BB20" si="24">+AR20*1.05</f>
+      <c r="AU20" s="2">
+        <f t="shared" ref="AU20:BD20" si="24">+AT20*1.05</f>
         <v>192.03455250000002</v>
       </c>
-      <c r="AT20" s="2">
+      <c r="AV20" s="2">
         <f t="shared" si="24"/>
         <v>201.63628012500004</v>
       </c>
-      <c r="AU20" s="2">
+      <c r="AW20" s="2">
         <f t="shared" si="24"/>
         <v>211.71809413125004</v>
       </c>
-      <c r="AV20" s="2">
+      <c r="AX20" s="2">
         <f t="shared" si="24"/>
         <v>222.30399883781254</v>
       </c>
-      <c r="AW20" s="2">
+      <c r="AY20" s="2">
         <f t="shared" si="24"/>
         <v>233.41919877970318</v>
       </c>
-      <c r="AX20" s="2">
+      <c r="AZ20" s="2">
         <f t="shared" si="24"/>
         <v>245.09015871868834</v>
       </c>
-      <c r="AY20" s="2">
+      <c r="BA20" s="2">
         <f t="shared" si="24"/>
         <v>257.34466665462276</v>
       </c>
-      <c r="AZ20" s="2">
+      <c r="BB20" s="2">
         <f t="shared" si="24"/>
         <v>270.21189998735389</v>
       </c>
-      <c r="BA20" s="2">
+      <c r="BC20" s="2">
         <f t="shared" si="24"/>
         <v>283.72249498672159</v>
       </c>
-      <c r="BB20" s="2">
+      <c r="BD20" s="2">
         <f t="shared" si="24"/>
         <v>297.90861973605769</v>
       </c>
     </row>
-    <row r="21" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>41</v>
       </c>
@@ -3338,79 +3441,83 @@
       </c>
       <c r="AB21" s="7">
         <f t="shared" si="25"/>
-        <v>0</v>
+        <v>589.96900000000005</v>
       </c>
       <c r="AC21" s="7">
-        <f t="shared" ref="AC21:AD21" si="26">AC18+AC19+AC20</f>
-        <v>0</v>
+        <f t="shared" ref="AC21:AE21" si="26">AC18+AC19+AC20</f>
+        <v>610.42900000000009</v>
       </c>
       <c r="AD21" s="7">
         <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="AM21" s="2"/>
-      <c r="AN21" s="2">
-        <f>SUM(AN18:AN20)</f>
+        <v>652.13600000000008</v>
+      </c>
+      <c r="AE21" s="7">
+        <f t="shared" si="26"/>
+        <v>695</v>
+      </c>
+      <c r="AO21" s="2"/>
+      <c r="AP21" s="2">
+        <f>SUM(AP18:AP20)</f>
         <v>922.58999999999992</v>
       </c>
-      <c r="AO21" s="2">
-        <f>SUM(AO18:AO20)</f>
+      <c r="AQ21" s="2">
+        <f>SUM(AQ18:AQ20)</f>
         <v>1288.242</v>
       </c>
-      <c r="AP21" s="2">
-        <f t="shared" ref="AP21:AQ21" si="27">SUM(AP18:AP20)</f>
+      <c r="AR21" s="2">
+        <f t="shared" ref="AR21:AS21" si="27">SUM(AR18:AR20)</f>
         <v>1790.1130000000001</v>
       </c>
-      <c r="AQ21" s="2">
+      <c r="AS21" s="2">
         <f t="shared" si="27"/>
         <v>2025.895</v>
       </c>
-      <c r="AR21" s="2">
-        <f t="shared" ref="AR21" si="28">SUM(AR18:AR20)</f>
+      <c r="AT21" s="2">
+        <f t="shared" ref="AT21" si="28">SUM(AT18:AT20)</f>
         <v>2127.18975</v>
       </c>
-      <c r="AS21" s="2">
-        <f t="shared" ref="AS21" si="29">SUM(AS18:AS20)</f>
+      <c r="AU21" s="2">
+        <f t="shared" ref="AU21" si="29">SUM(AU18:AU20)</f>
         <v>2233.5492375000003</v>
       </c>
-      <c r="AT21" s="2">
-        <f t="shared" ref="AT21" si="30">SUM(AT18:AT20)</f>
+      <c r="AV21" s="2">
+        <f t="shared" ref="AV21" si="30">SUM(AV18:AV20)</f>
         <v>2345.2266993750004</v>
       </c>
-      <c r="AU21" s="2">
-        <f t="shared" ref="AU21" si="31">SUM(AU18:AU20)</f>
+      <c r="AW21" s="2">
+        <f t="shared" ref="AW21" si="31">SUM(AW18:AW20)</f>
         <v>2462.4880343437503</v>
       </c>
-      <c r="AV21" s="2">
-        <f t="shared" ref="AV21" si="32">SUM(AV18:AV20)</f>
+      <c r="AX21" s="2">
+        <f t="shared" ref="AX21" si="32">SUM(AX18:AX20)</f>
         <v>2585.6124360609383</v>
       </c>
-      <c r="AW21" s="2">
-        <f t="shared" ref="AW21" si="33">SUM(AW18:AW20)</f>
+      <c r="AY21" s="2">
+        <f t="shared" ref="AY21" si="33">SUM(AY18:AY20)</f>
         <v>2714.8930578639847</v>
       </c>
-      <c r="AX21" s="2">
-        <f t="shared" ref="AX21" si="34">SUM(AX18:AX20)</f>
+      <c r="AZ21" s="2">
+        <f t="shared" ref="AZ21" si="34">SUM(AZ18:AZ20)</f>
         <v>2850.6377107571843</v>
       </c>
-      <c r="AY21" s="2">
-        <f t="shared" ref="AY21" si="35">SUM(AY18:AY20)</f>
+      <c r="BA21" s="2">
+        <f t="shared" ref="BA21" si="35">SUM(BA18:BA20)</f>
         <v>2993.1695962950439</v>
       </c>
-      <c r="AZ21" s="2">
-        <f t="shared" ref="AZ21" si="36">SUM(AZ18:AZ20)</f>
+      <c r="BB21" s="2">
+        <f t="shared" ref="BB21" si="36">SUM(BB18:BB20)</f>
         <v>3142.8280761097958</v>
       </c>
-      <c r="BA21" s="2">
-        <f t="shared" ref="BA21" si="37">SUM(BA18:BA20)</f>
+      <c r="BC21" s="2">
+        <f t="shared" ref="BC21" si="37">SUM(BC18:BC20)</f>
         <v>3299.9694799152858</v>
       </c>
-      <c r="BB21" s="2">
-        <f t="shared" ref="BB21" si="38">SUM(BB18:BB20)</f>
+      <c r="BD21" s="2">
+        <f t="shared" ref="BD21" si="38">SUM(BD18:BD20)</f>
         <v>3464.9679539110502</v>
       </c>
     </row>
-    <row r="22" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>42</v>
       </c>
@@ -3472,79 +3579,83 @@
       </c>
       <c r="AB22" s="7">
         <f t="shared" si="39"/>
-        <v>1041.69</v>
+        <v>-322.46000000000026</v>
       </c>
       <c r="AC22" s="7">
-        <f t="shared" ref="AC22:AD22" si="40">AC17-AC21</f>
-        <v>1116.92875</v>
+        <f t="shared" ref="AC22:AE22" si="40">AC17-AC21</f>
+        <v>-296.53500000000008</v>
       </c>
       <c r="AD22" s="7">
         <f t="shared" si="40"/>
-        <v>1148.6912499999999</v>
-      </c>
-      <c r="AM22" s="2"/>
-      <c r="AN22" s="2">
-        <f>AN17-AN21</f>
+        <v>-358.63800000000026</v>
+      </c>
+      <c r="AE22" s="7">
+        <f t="shared" si="40"/>
+        <v>-294</v>
+      </c>
+      <c r="AO22" s="2"/>
+      <c r="AP22" s="2">
+        <f>AP17-AP21</f>
         <v>-571.80700000000002</v>
       </c>
-      <c r="AO22" s="2">
-        <f>AO17-AO21</f>
+      <c r="AQ22" s="2">
+        <f>AQ17-AQ21</f>
         <v>-923.78399999999988</v>
       </c>
-      <c r="AP22" s="2">
-        <f t="shared" ref="AP22:AQ22" si="41">AP17-AP21</f>
+      <c r="AR22" s="2">
+        <f t="shared" ref="AR22:AS22" si="41">AR17-AR21</f>
         <v>-1259.0330000000001</v>
       </c>
-      <c r="AQ22" s="2">
+      <c r="AS22" s="2">
         <f t="shared" si="41"/>
         <v>-1063.3170000000005</v>
       </c>
-      <c r="AR22" s="2">
-        <f t="shared" ref="AR22" si="42">AR17-AR21</f>
-        <v>-607.30880000000025</v>
-      </c>
-      <c r="AS22" s="2">
-        <f t="shared" ref="AS22" si="43">AS17-AS21</f>
-        <v>-62.290737500000432</v>
-      </c>
       <c r="AT22" s="2">
-        <f t="shared" ref="AT22" si="44">AT17-AT21</f>
-        <v>708.10556624999936</v>
+        <f t="shared" ref="AT22" si="42">AT17-AT21</f>
+        <v>-415.49690000000032</v>
       </c>
       <c r="AU22" s="2">
-        <f t="shared" ref="AU22" si="45">AU17-AU21</f>
-        <v>1778.2512234687497</v>
+        <f t="shared" ref="AU22" si="43">AU17-AU21</f>
+        <v>211.72626249999939</v>
       </c>
       <c r="AV22" s="2">
-        <f t="shared" ref="AV22" si="46">AV17-AV21</f>
-        <v>3245.4040434312501</v>
+        <f t="shared" ref="AV22" si="44">AV17-AV21</f>
+        <v>1093.4419724999993</v>
       </c>
       <c r="AW22" s="2">
-        <f t="shared" ref="AW22" si="47">AW17-AW21</f>
-        <v>4536.7710729953897</v>
+        <f t="shared" ref="AW22" si="45">AW17-AW21</f>
+        <v>2313.4406765937497</v>
       </c>
       <c r="AX22" s="2">
-        <f t="shared" ref="AX22" si="48">AX17-AX21</f>
-        <v>5546.0260197115658</v>
+        <f t="shared" ref="AX22" si="46">AX17-AX21</f>
+        <v>3981.2895414781251</v>
       </c>
       <c r="AY22" s="2">
-        <f t="shared" ref="AY22" si="49">AY17-AY21</f>
-        <v>6243.1605072205821</v>
+        <f t="shared" ref="AY22" si="47">AY17-AY21</f>
+        <v>5451.9450378391393</v>
       </c>
       <c r="AZ22" s="2">
-        <f t="shared" ref="AZ22" si="50">AZ17-AZ21</f>
-        <v>7017.1350377573945</v>
+        <f t="shared" ref="AZ22" si="48">AZ17-AZ21</f>
+        <v>6605.7011368990661</v>
       </c>
       <c r="BA22" s="2">
-        <f t="shared" ref="BA22" si="51">BA17-BA21</f>
-        <v>7875.9899453386224</v>
+        <f t="shared" ref="BA22" si="49">BA17-BA21</f>
+        <v>7408.8031361268331</v>
       </c>
       <c r="BB22" s="2">
-        <f t="shared" ref="BB22" si="52">BB17-BB21</f>
-        <v>8828.587413868252</v>
-      </c>
-    </row>
-    <row r="23" spans="2:54" x14ac:dyDescent="0.25">
+        <f t="shared" ref="BB22" si="50">BB17-BB21</f>
+        <v>8299.3419295542681</v>
+      </c>
+      <c r="BC22" s="2">
+        <f t="shared" ref="BC22" si="51">BC17-BC21</f>
+        <v>9286.4175263151865</v>
+      </c>
+      <c r="BD22" s="2">
+        <f t="shared" ref="BD22" si="52">BD17-BD21</f>
+        <v>10380.05775294247</v>
+      </c>
+    </row>
+    <row r="23" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>32</v>
       </c>
@@ -3552,25 +3663,25 @@
       <c r="V23" s="2"/>
       <c r="W23" s="2"/>
       <c r="X23" s="2"/>
-      <c r="AM23" s="2">
+      <c r="AO23" s="2">
         <v>600.17700000000002</v>
       </c>
-      <c r="AN23" s="2">
+      <c r="AP23" s="2">
         <v>673.92600000000004</v>
       </c>
-      <c r="AO23" s="2">
+      <c r="AQ23" s="2">
         <v>356.45600000000002</v>
       </c>
-      <c r="AP23" s="13">
-        <f t="shared" ref="AP23" si="53">SUM(S23:V23)</f>
+      <c r="AR23" s="2">
+        <f t="shared" ref="AR23" si="53">SUM(S23:V23)</f>
         <v>0</v>
       </c>
-      <c r="AQ23" s="13">
-        <f t="shared" ref="AQ23" si="54">SUM(W23:Z23)</f>
+      <c r="AS23" s="2">
+        <f t="shared" ref="AS23" si="54">SUM(W23:Z23)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>43</v>
       </c>
@@ -3602,36 +3713,44 @@
         <f>+Z24</f>
         <v>35.929000000000002</v>
       </c>
-      <c r="AN24">
+      <c r="AB24">
+        <f>48.844-10.342</f>
+        <v>38.502000000000002</v>
+      </c>
+      <c r="AC24" s="2">
+        <f>52.089-10.352</f>
+        <v>41.736999999999995</v>
+      </c>
+      <c r="AD24" s="2">
+        <f>54.354-10.413</f>
+        <v>43.941000000000003</v>
+      </c>
+      <c r="AE24">
+        <f>55-10+2</f>
+        <v>47</v>
+      </c>
+      <c r="AP24">
         <f>-6.998-1.796</f>
         <v>-8.7940000000000005</v>
       </c>
-      <c r="AO24" s="2">
+      <c r="AQ24" s="2">
         <f>38.842-39.903-5.744</f>
         <v>-6.8049999999999997</v>
       </c>
-      <c r="AP24" s="13">
-        <f t="shared" ref="AP24" si="55">SUM(S24:V24)</f>
+      <c r="AR24" s="2">
+        <f t="shared" ref="AR24" si="55">SUM(S24:V24)</f>
         <v>-19.852</v>
       </c>
-      <c r="AQ24" s="13">
-        <f t="shared" ref="AQ24" si="56">SUM(W24:Z24)</f>
+      <c r="AS24" s="2">
+        <f t="shared" ref="AS24" si="56">SUM(W24:Z24)</f>
         <v>50.484999999999999</v>
       </c>
-      <c r="AR24" s="2">
-        <f>+AQ24</f>
+      <c r="AT24" s="2">
+        <f>+AS24</f>
         <v>50.484999999999999</v>
       </c>
-      <c r="AS24" s="2">
-        <f t="shared" ref="AS24:BB24" si="57">+AR24</f>
-        <v>50.484999999999999</v>
-      </c>
-      <c r="AT24" s="2">
-        <f t="shared" si="57"/>
-        <v>50.484999999999999</v>
-      </c>
       <c r="AU24" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" ref="AU24:BD24" si="57">+AT24</f>
         <v>50.484999999999999</v>
       </c>
       <c r="AV24" s="2">
@@ -3662,8 +3781,16 @@
         <f t="shared" si="57"/>
         <v>50.484999999999999</v>
       </c>
-    </row>
-    <row r="25" spans="2:54" x14ac:dyDescent="0.25">
+      <c r="BC24" s="2">
+        <f t="shared" si="57"/>
+        <v>50.484999999999999</v>
+      </c>
+      <c r="BD24" s="2">
+        <f t="shared" si="57"/>
+        <v>50.484999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>44</v>
       </c>
@@ -3684,103 +3811,107 @@
         <v>-300.29899999999998</v>
       </c>
       <c r="V25" s="2">
-        <f>+V22+V24</f>
+        <f t="shared" ref="V25:AE25" si="58">+V22+V24</f>
         <v>-364.59299999999996</v>
       </c>
       <c r="W25" s="2">
-        <f>+W22+W24</f>
+        <f t="shared" si="58"/>
         <v>-313.03700000000009</v>
       </c>
       <c r="X25" s="2">
-        <f>+X22+X24</f>
+        <f t="shared" si="58"/>
         <v>-251.46800000000002</v>
       </c>
       <c r="Y25" s="2">
-        <f>+Y22+Y24</f>
+        <f t="shared" si="58"/>
         <v>-240.14400000000012</v>
       </c>
       <c r="Z25" s="2">
-        <f>+Z22+Z24</f>
+        <f t="shared" si="58"/>
         <v>-208.18299999999996</v>
       </c>
       <c r="AA25" s="2">
-        <f>+AA22+AA24</f>
+        <f t="shared" si="58"/>
         <v>-218.77999999999994</v>
       </c>
       <c r="AB25" s="2">
-        <f>+AB22+AB24</f>
-        <v>1041.69</v>
+        <f t="shared" si="58"/>
+        <v>-283.95800000000025</v>
       </c>
       <c r="AC25" s="2">
-        <f>+AC22+AC24</f>
-        <v>1116.92875</v>
+        <f t="shared" si="58"/>
+        <v>-254.79800000000009</v>
       </c>
       <c r="AD25" s="2">
-        <f>+AD22+AD24</f>
-        <v>1148.6912499999999</v>
-      </c>
-      <c r="AN25" s="2">
-        <f>+AN22+AN24</f>
+        <f t="shared" si="58"/>
+        <v>-314.69700000000023</v>
+      </c>
+      <c r="AE25" s="2">
+        <f t="shared" si="58"/>
+        <v>-247</v>
+      </c>
+      <c r="AP25" s="2">
+        <f>+AP22+AP24</f>
         <v>-580.601</v>
       </c>
-      <c r="AO25" s="2">
-        <f>+AO22+AO24</f>
+      <c r="AQ25" s="2">
+        <f>+AQ22+AQ24</f>
         <v>-930.58899999999983</v>
       </c>
-      <c r="AP25" s="2">
-        <f t="shared" ref="AP25:AQ25" si="58">+AP22+AP24</f>
+      <c r="AR25" s="2">
+        <f t="shared" ref="AR25:AS25" si="59">+AR22+AR24</f>
         <v>-1278.8850000000002</v>
       </c>
-      <c r="AQ25" s="2">
-        <f t="shared" si="58"/>
+      <c r="AS25" s="2">
+        <f t="shared" si="59"/>
         <v>-1012.8320000000004</v>
       </c>
-      <c r="AR25" s="2">
-        <f t="shared" ref="AR25" si="59">+AR22+AR24</f>
-        <v>-556.82380000000023</v>
-      </c>
-      <c r="AS25" s="2">
-        <f t="shared" ref="AS25" si="60">+AS22+AS24</f>
-        <v>-11.805737500000433</v>
-      </c>
       <c r="AT25" s="2">
-        <f t="shared" ref="AT25" si="61">+AT22+AT24</f>
-        <v>758.59056624999937</v>
+        <f t="shared" ref="AT25" si="60">+AT22+AT24</f>
+        <v>-365.01190000000031</v>
       </c>
       <c r="AU25" s="2">
-        <f t="shared" ref="AU25" si="62">+AU22+AU24</f>
-        <v>1828.7362234687496</v>
+        <f t="shared" ref="AU25" si="61">+AU22+AU24</f>
+        <v>262.21126249999941</v>
       </c>
       <c r="AV25" s="2">
-        <f t="shared" ref="AV25" si="63">+AV22+AV24</f>
-        <v>3295.8890434312502</v>
+        <f t="shared" ref="AV25" si="62">+AV22+AV24</f>
+        <v>1143.9269724999992</v>
       </c>
       <c r="AW25" s="2">
-        <f t="shared" ref="AW25" si="64">+AW22+AW24</f>
-        <v>4587.2560729953893</v>
+        <f t="shared" ref="AW25" si="63">+AW22+AW24</f>
+        <v>2363.9256765937498</v>
       </c>
       <c r="AX25" s="2">
-        <f t="shared" ref="AX25" si="65">+AX22+AX24</f>
-        <v>5596.5110197115655</v>
+        <f t="shared" ref="AX25" si="64">+AX22+AX24</f>
+        <v>4031.7745414781252</v>
       </c>
       <c r="AY25" s="2">
-        <f t="shared" ref="AY25" si="66">+AY22+AY24</f>
-        <v>6293.6455072205817</v>
+        <f t="shared" ref="AY25" si="65">+AY22+AY24</f>
+        <v>5502.430037839139</v>
       </c>
       <c r="AZ25" s="2">
-        <f t="shared" ref="AZ25" si="67">+AZ22+AZ24</f>
-        <v>7067.6200377573941</v>
+        <f t="shared" ref="AZ25" si="66">+AZ22+AZ24</f>
+        <v>6656.1861368990658</v>
       </c>
       <c r="BA25" s="2">
-        <f t="shared" ref="BA25" si="68">+BA22+BA24</f>
-        <v>7926.4749453386221</v>
+        <f t="shared" ref="BA25" si="67">+BA22+BA24</f>
+        <v>7459.2881361268328</v>
       </c>
       <c r="BB25" s="2">
-        <f t="shared" ref="BB25" si="69">+BB22+BB24</f>
-        <v>8879.0724138682526</v>
-      </c>
-    </row>
-    <row r="26" spans="2:54" x14ac:dyDescent="0.25">
+        <f t="shared" ref="BB25" si="68">+BB22+BB24</f>
+        <v>8349.8269295542686</v>
+      </c>
+      <c r="BC25" s="2">
+        <f t="shared" ref="BC25" si="69">+BC22+BC24</f>
+        <v>9336.9025263151871</v>
+      </c>
+      <c r="BD25" s="2">
+        <f t="shared" ref="BD25" si="70">+BD22+BD24</f>
+        <v>10430.542752942471</v>
+      </c>
+    </row>
+    <row r="26" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>45</v>
       </c>
@@ -3810,67 +3941,79 @@
       <c r="AA26" s="2">
         <v>0</v>
       </c>
-      <c r="AN26">
+      <c r="AB26" s="2">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="AC26" s="2">
+        <v>0.80300000000000005</v>
+      </c>
+      <c r="AD26" s="2">
+        <v>-2.456</v>
+      </c>
+      <c r="AE26">
+        <v>1</v>
+      </c>
+      <c r="AP26">
         <v>-11.829000000000001</v>
       </c>
-      <c r="AO26" s="2">
+      <c r="AQ26" s="2">
         <f>3.552-9.775</f>
         <v>-6.2230000000000008</v>
       </c>
-      <c r="AP26" s="13">
-        <f t="shared" ref="AP26" si="70">SUM(S26:V26)</f>
+      <c r="AR26" s="2">
+        <f t="shared" ref="AR26" si="71">SUM(S26:V26)</f>
         <v>1.008</v>
       </c>
-      <c r="AQ26" s="13">
-        <f t="shared" ref="AQ26" si="71">SUM(W26:Z26)</f>
+      <c r="AS26" s="2">
+        <f t="shared" ref="AS26" si="72">SUM(W26:Z26)</f>
         <v>2.9510000000000001</v>
       </c>
-      <c r="AR26" s="2">
-        <f>+AR25*0.1</f>
-        <v>-55.682380000000023</v>
-      </c>
-      <c r="AS26" s="2">
-        <f t="shared" ref="AS26:BB26" si="72">+AS25*0.1</f>
-        <v>-1.1805737500000433</v>
-      </c>
       <c r="AT26" s="2">
-        <f t="shared" si="72"/>
-        <v>75.859056624999937</v>
+        <f>+AT25*0.1</f>
+        <v>-36.50119000000003</v>
       </c>
       <c r="AU26" s="2">
-        <f t="shared" si="72"/>
-        <v>182.87362234687498</v>
+        <f t="shared" ref="AU26:BD26" si="73">+AU25*0.1</f>
+        <v>26.221126249999941</v>
       </c>
       <c r="AV26" s="2">
-        <f t="shared" si="72"/>
-        <v>329.58890434312502</v>
+        <f t="shared" si="73"/>
+        <v>114.39269724999993</v>
       </c>
       <c r="AW26" s="2">
-        <f t="shared" si="72"/>
-        <v>458.72560729953898</v>
+        <f t="shared" si="73"/>
+        <v>236.392567659375</v>
       </c>
       <c r="AX26" s="2">
-        <f t="shared" si="72"/>
-        <v>559.65110197115655</v>
+        <f t="shared" si="73"/>
+        <v>403.17745414781257</v>
       </c>
       <c r="AY26" s="2">
-        <f t="shared" si="72"/>
-        <v>629.3645507220582</v>
+        <f t="shared" si="73"/>
+        <v>550.24300378391388</v>
       </c>
       <c r="AZ26" s="2">
-        <f t="shared" si="72"/>
-        <v>706.76200377573946</v>
+        <f t="shared" si="73"/>
+        <v>665.61861368990662</v>
       </c>
       <c r="BA26" s="2">
-        <f t="shared" si="72"/>
-        <v>792.6474945338623</v>
+        <f t="shared" si="73"/>
+        <v>745.92881361268337</v>
       </c>
       <c r="BB26" s="2">
-        <f t="shared" si="72"/>
-        <v>887.90724138682526</v>
-      </c>
-    </row>
-    <row r="27" spans="2:54" x14ac:dyDescent="0.25">
+        <f t="shared" si="73"/>
+        <v>834.98269295542696</v>
+      </c>
+      <c r="BC26" s="2">
+        <f t="shared" si="73"/>
+        <v>933.69025263151877</v>
+      </c>
+      <c r="BD26" s="2">
+        <f t="shared" si="73"/>
+        <v>1043.0542752942472</v>
+      </c>
+    </row>
+    <row r="27" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>46</v>
       </c>
@@ -3891,103 +4034,107 @@
         <v>-301.02999999999997</v>
       </c>
       <c r="V27" s="2">
-        <f>+V25-V26</f>
+        <f t="shared" ref="V27:AE27" si="74">+V25-V26</f>
         <v>-364.86999999999995</v>
       </c>
       <c r="W27" s="2">
-        <f>+W25-W26</f>
+        <f t="shared" si="74"/>
         <v>-313.03700000000009</v>
       </c>
       <c r="X27" s="2">
-        <f>+X25-X26</f>
+        <f t="shared" si="74"/>
         <v>-251.46800000000002</v>
       </c>
       <c r="Y27" s="2">
-        <f>+Y25-Y26</f>
+        <f t="shared" si="74"/>
         <v>-240.44700000000012</v>
       </c>
       <c r="Z27" s="2">
-        <f>+Z25-Z26</f>
+        <f t="shared" si="74"/>
         <v>-210.83099999999996</v>
       </c>
       <c r="AA27" s="2">
-        <f>+AA25-AA26</f>
+        <f t="shared" si="74"/>
         <v>-218.77999999999994</v>
       </c>
       <c r="AB27" s="2">
-        <f>+AB25-AB26</f>
-        <v>1041.69</v>
+        <f t="shared" si="74"/>
+        <v>-284.93100000000027</v>
       </c>
       <c r="AC27" s="2">
-        <f>+AC25-AC26</f>
-        <v>1116.92875</v>
+        <f t="shared" si="74"/>
+        <v>-255.60100000000008</v>
       </c>
       <c r="AD27" s="2">
-        <f>+AD25-AD26</f>
-        <v>1148.6912499999999</v>
-      </c>
-      <c r="AN27" s="2">
-        <f>+AN25-AN26</f>
-        <v>-568.77200000000005</v>
-      </c>
-      <c r="AO27" s="2">
-        <f>+AO25-AO26</f>
-        <v>-924.36599999999987</v>
+        <f t="shared" si="74"/>
+        <v>-312.24100000000021</v>
+      </c>
+      <c r="AE27" s="2">
+        <f t="shared" si="74"/>
+        <v>-248</v>
       </c>
       <c r="AP27" s="2">
         <f>+AP25-AP26</f>
-        <v>-1279.8930000000003</v>
+        <v>-568.77200000000005</v>
       </c>
       <c r="AQ27" s="2">
         <f>+AQ25-AQ26</f>
+        <v>-924.36599999999987</v>
+      </c>
+      <c r="AR27" s="2">
+        <f>+AR25-AR26</f>
+        <v>-1279.8930000000003</v>
+      </c>
+      <c r="AS27" s="2">
+        <f>+AS25-AS26</f>
         <v>-1015.7830000000005</v>
       </c>
-      <c r="AR27" s="2">
-        <f t="shared" ref="AR27:BB27" si="73">+AR25-AR26</f>
-        <v>-501.14142000000021</v>
-      </c>
-      <c r="AS27" s="2">
-        <f t="shared" si="73"/>
-        <v>-10.625163750000389</v>
-      </c>
       <c r="AT27" s="2">
-        <f t="shared" si="73"/>
-        <v>682.73150962499949</v>
+        <f t="shared" ref="AT27:BD27" si="75">+AT25-AT26</f>
+        <v>-328.5107100000003</v>
       </c>
       <c r="AU27" s="2">
-        <f t="shared" si="73"/>
-        <v>1645.8626011218746</v>
+        <f t="shared" si="75"/>
+        <v>235.99013624999947</v>
       </c>
       <c r="AV27" s="2">
-        <f t="shared" si="73"/>
-        <v>2966.3001390881254</v>
+        <f t="shared" si="75"/>
+        <v>1029.5342752499994</v>
       </c>
       <c r="AW27" s="2">
-        <f t="shared" si="73"/>
-        <v>4128.5304656958506</v>
+        <f t="shared" si="75"/>
+        <v>2127.5331089343749</v>
       </c>
       <c r="AX27" s="2">
-        <f t="shared" si="73"/>
-        <v>5036.8599177404085</v>
+        <f t="shared" si="75"/>
+        <v>3628.5970873303127</v>
       </c>
       <c r="AY27" s="2">
-        <f t="shared" si="73"/>
-        <v>5664.2809564985237</v>
+        <f t="shared" si="75"/>
+        <v>4952.187034055225</v>
       </c>
       <c r="AZ27" s="2">
-        <f t="shared" si="73"/>
-        <v>6360.8580339816544</v>
+        <f t="shared" si="75"/>
+        <v>5990.5675232091589</v>
       </c>
       <c r="BA27" s="2">
-        <f t="shared" si="73"/>
-        <v>7133.8274508047598</v>
+        <f t="shared" si="75"/>
+        <v>6713.3593225141494</v>
       </c>
       <c r="BB27" s="2">
-        <f t="shared" si="73"/>
-        <v>7991.1651724814274</v>
-      </c>
-    </row>
-    <row r="28" spans="2:54" x14ac:dyDescent="0.25">
+        <f t="shared" si="75"/>
+        <v>7514.8442365988412</v>
+      </c>
+      <c r="BC27" s="2">
+        <f t="shared" si="75"/>
+        <v>8403.2122736836682</v>
+      </c>
+      <c r="BD27" s="2">
+        <f t="shared" si="75"/>
+        <v>9387.4884776482231</v>
+      </c>
+    </row>
+    <row r="28" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>47</v>
       </c>
@@ -4008,103 +4155,107 @@
         <v>-0.49622756277642149</v>
       </c>
       <c r="V28" s="1">
-        <f>+V27/V29</f>
+        <f t="shared" ref="V28:AE28" si="76">+V27/V29</f>
         <v>-0.58209971969490293</v>
       </c>
       <c r="W28" s="1">
-        <f>+W27/W29</f>
+        <f t="shared" si="76"/>
         <v>-0.49295612736606736</v>
       </c>
       <c r="X28" s="1">
-        <f>+X27/X29</f>
+        <f t="shared" si="76"/>
         <v>-0.39119869822374753</v>
       </c>
       <c r="Y28" s="1">
-        <f>+Y27/Y29</f>
+        <f t="shared" si="76"/>
         <v>-0.36937235871273411</v>
       </c>
       <c r="Z28" s="1">
-        <f>+Z27/Z29</f>
+        <f t="shared" si="76"/>
         <v>-0.31900590104403082</v>
       </c>
       <c r="AA28" s="1">
-        <f>+AA27/AA29</f>
+        <f t="shared" si="76"/>
         <v>-0.32573173509693182</v>
       </c>
       <c r="AB28" s="1">
-        <f>+AB27/AB29</f>
-        <v>1.5509255468192842</v>
+        <f t="shared" si="76"/>
+        <v>-0.4160566674989819</v>
       </c>
       <c r="AC28" s="1">
-        <f>+AC27/AC29</f>
-        <v>1.6629451490865128</v>
+        <f t="shared" si="76"/>
+        <v>-0.36656761539807436</v>
       </c>
       <c r="AD28" s="1">
-        <f>+AD27/AD29</f>
-        <v>1.7102349115694466</v>
-      </c>
-      <c r="AN28" s="1">
-        <f>+AN27/AN29</f>
-        <v>-1.1243708708768074</v>
-      </c>
-      <c r="AO28" s="1">
-        <f>+AO27/AO29</f>
-        <v>-1.5520981128653919</v>
+        <f t="shared" si="76"/>
+        <v>-0.44304145909215414</v>
+      </c>
+      <c r="AE28" s="1">
+        <f t="shared" si="76"/>
+        <v>-0.34846289923942353</v>
       </c>
       <c r="AP28" s="1">
         <f>+AP27/AP29</f>
-        <v>-2.0752991193834553</v>
+        <v>-1.1243708708768074</v>
       </c>
       <c r="AQ28" s="1">
         <f>+AQ27/AQ29</f>
-        <v>-1.5689615958636065</v>
+        <v>-1.5520981128653919</v>
       </c>
       <c r="AR28" s="1">
         <f>+AR27/AR29</f>
-        <v>-0.77405473617549603</v>
+        <v>-2.0752991193834553</v>
       </c>
       <c r="AS28" s="1">
-        <f t="shared" ref="AS28:BB28" si="74">+AS27/AS29</f>
-        <v>-1.6411451927737266E-2</v>
+        <f>+AS27/AS29</f>
+        <v>-1.5689615958636065</v>
       </c>
       <c r="AT28" s="1">
-        <f t="shared" si="74"/>
-        <v>1.0545357806614286</v>
+        <f>+AT27/AT29</f>
+        <v>-0.50741220105070339</v>
       </c>
       <c r="AU28" s="1">
-        <f t="shared" si="74"/>
-        <v>2.5421721108035884</v>
+        <f t="shared" ref="AU28:BD28" si="77">+AU27/AU29</f>
+        <v>0.36450645539339499</v>
       </c>
       <c r="AV28" s="1">
-        <f t="shared" si="74"/>
-        <v>4.5816980595601038</v>
+        <f t="shared" si="77"/>
+        <v>1.590201587831771</v>
       </c>
       <c r="AW28" s="1">
-        <f t="shared" si="74"/>
-        <v>6.3768597702754199</v>
+        <f t="shared" si="77"/>
+        <v>3.2861523985401759</v>
       </c>
       <c r="AX28" s="1">
-        <f t="shared" si="74"/>
-        <v>7.779850395881228</v>
+        <f t="shared" si="77"/>
+        <v>5.6046709551979106</v>
       </c>
       <c r="AY28" s="1">
-        <f t="shared" si="74"/>
-        <v>8.7489545394319013</v>
+        <f t="shared" si="77"/>
+        <v>7.6490660623049829</v>
       </c>
       <c r="AZ28" s="1">
-        <f t="shared" si="74"/>
-        <v>9.8248759548621063</v>
+        <f t="shared" si="77"/>
+        <v>9.2529313655996699</v>
       </c>
       <c r="BA28" s="1">
-        <f t="shared" si="74"/>
-        <v>11.018791712236013</v>
+        <f t="shared" si="77"/>
+        <v>10.369343606122188</v>
       </c>
       <c r="BB28" s="1">
-        <f t="shared" si="74"/>
-        <v>12.343021355768039</v>
-      </c>
-    </row>
-    <row r="29" spans="2:54" x14ac:dyDescent="0.25">
+        <f t="shared" si="77"/>
+        <v>11.60730392822142</v>
+      </c>
+      <c r="BC28" s="1">
+        <f t="shared" si="77"/>
+        <v>12.979462482931263</v>
+      </c>
+      <c r="BD28" s="1">
+        <f t="shared" si="77"/>
+        <v>14.499759203532809</v>
+      </c>
+    </row>
+    <row r="29" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>1</v>
       </c>
@@ -4139,372 +4290,380 @@
         <v>671.65700000000004</v>
       </c>
       <c r="AB29" s="2">
-        <f>+AA29</f>
-        <v>671.65700000000004</v>
+        <v>684.83699999999999</v>
       </c>
       <c r="AC29" s="2">
-        <f>+AB29</f>
-        <v>671.65700000000004</v>
+        <v>697.28200000000004</v>
       </c>
       <c r="AD29" s="2">
-        <f>+AC29</f>
-        <v>671.65700000000004</v>
-      </c>
-      <c r="AN29" s="2">
+        <v>704.76700000000005</v>
+      </c>
+      <c r="AE29" s="2">
+        <v>711.697</v>
+      </c>
+      <c r="AP29" s="2">
         <v>505.858</v>
       </c>
-      <c r="AO29" s="2">
+      <c r="AQ29" s="2">
         <v>595.55899999999997</v>
       </c>
-      <c r="AP29" s="2">
+      <c r="AR29" s="2">
         <f>AVERAGE(S29:V29)</f>
         <v>616.72699999999998</v>
       </c>
-      <c r="AQ29" s="2">
+      <c r="AS29" s="2">
         <f>AVERAGE(W29:Z29)</f>
         <v>647.42374999999993</v>
       </c>
-      <c r="AR29" s="2">
-        <f>+AQ29</f>
+      <c r="AT29" s="2">
+        <f>+AS29</f>
         <v>647.42374999999993</v>
       </c>
-      <c r="AS29" s="2">
-        <f t="shared" ref="AS29:BB29" si="75">+AR29</f>
+      <c r="AU29" s="2">
+        <f t="shared" ref="AU29:BD29" si="78">+AT29</f>
         <v>647.42374999999993</v>
       </c>
-      <c r="AT29" s="2">
-        <f t="shared" si="75"/>
+      <c r="AV29" s="2">
+        <f t="shared" si="78"/>
         <v>647.42374999999993</v>
       </c>
-      <c r="AU29" s="2">
-        <f t="shared" si="75"/>
+      <c r="AW29" s="2">
+        <f t="shared" si="78"/>
         <v>647.42374999999993</v>
       </c>
-      <c r="AV29" s="2">
-        <f t="shared" si="75"/>
+      <c r="AX29" s="2">
+        <f t="shared" si="78"/>
         <v>647.42374999999993</v>
       </c>
-      <c r="AW29" s="2">
-        <f t="shared" si="75"/>
+      <c r="AY29" s="2">
+        <f t="shared" si="78"/>
         <v>647.42374999999993</v>
       </c>
-      <c r="AX29" s="2">
-        <f t="shared" si="75"/>
+      <c r="AZ29" s="2">
+        <f t="shared" si="78"/>
         <v>647.42374999999993</v>
       </c>
-      <c r="AY29" s="2">
-        <f t="shared" si="75"/>
+      <c r="BA29" s="2">
+        <f t="shared" si="78"/>
         <v>647.42374999999993</v>
       </c>
-      <c r="AZ29" s="2">
-        <f t="shared" si="75"/>
+      <c r="BB29" s="2">
+        <f t="shared" si="78"/>
         <v>647.42374999999993</v>
       </c>
-      <c r="BA29" s="2">
-        <f t="shared" si="75"/>
+      <c r="BC29" s="2">
+        <f t="shared" si="78"/>
         <v>647.42374999999993</v>
       </c>
-      <c r="BB29" s="2">
-        <f t="shared" si="75"/>
+      <c r="BD29" s="2">
+        <f t="shared" si="78"/>
         <v>647.42374999999993</v>
       </c>
     </row>
-    <row r="30" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:56" x14ac:dyDescent="0.25">
       <c r="S30"/>
     </row>
-    <row r="31" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>48</v>
       </c>
       <c r="Q31" s="5">
-        <f t="shared" ref="Q31" si="76">Q12/M12-1</f>
+        <f t="shared" ref="Q31" si="79">Q12/M12-1</f>
         <v>1.6435123376317362E-2</v>
       </c>
       <c r="R31" s="5">
-        <f t="shared" ref="R31:AD31" si="77">R12/N12-1</f>
+        <f t="shared" ref="R31:AE31" si="80">R12/N12-1</f>
         <v>1.798797051175427E-2</v>
       </c>
       <c r="S31" s="5" t="e">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T31" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>0.15154252233143373</v>
       </c>
       <c r="U31" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>0.37766149578815833</v>
       </c>
       <c r="V31" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>0.29523143350604486</v>
       </c>
       <c r="W31" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>0.22271661905808227</v>
       </c>
       <c r="X31" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>0.31248971797884861</v>
       </c>
       <c r="Y31" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>0.28844754460373645</v>
       </c>
       <c r="Z31" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>0.31768450500640721</v>
       </c>
       <c r="AA31" s="5">
-        <f t="shared" si="77"/>
+        <f t="shared" si="80"/>
         <v>0.29190939722950238</v>
       </c>
       <c r="AB31" s="5">
-        <f t="shared" si="77"/>
-        <v>0.16579728116050374</v>
+        <f t="shared" si="80"/>
+        <v>0.20942920486199301</v>
       </c>
       <c r="AC31" s="5">
-        <f t="shared" si="77"/>
-        <v>0.21543620838062449</v>
+        <f t="shared" si="80"/>
+        <v>0.47955989044053404</v>
       </c>
       <c r="AD31" s="5">
-        <f t="shared" si="77"/>
-        <v>0.16242765763021616</v>
-      </c>
-      <c r="AN31" s="10">
-        <f>+AN12/AM12-1</f>
-        <v>1.0772942519902369</v>
-      </c>
-      <c r="AO31" s="10">
-        <f>+AO12/AN12-1</f>
-        <v>0.15937579623808285</v>
+        <f t="shared" si="80"/>
+        <v>0.43194226170658667</v>
+      </c>
+      <c r="AE31" s="5">
+        <f t="shared" si="80"/>
+        <v>0.39295812335117497</v>
       </c>
       <c r="AP31" s="10">
         <f>+AP12/AO12-1</f>
-        <v>0.25808655258393953</v>
+        <v>1.0772942519902369</v>
       </c>
       <c r="AQ31" s="10">
         <f>+AQ12/AP12-1</f>
-        <v>0.28673907980115088</v>
+        <v>0.15937579623808285</v>
       </c>
       <c r="AR31" s="10">
         <f>+AR12/AQ12-1</f>
-        <v>0.20559198151904834</v>
+        <v>0.25808655258393953</v>
       </c>
       <c r="AS31" s="10">
-        <f t="shared" ref="AS31:BB31" si="78">+AS12/AR12-1</f>
+        <f>+AS12/AR12-1</f>
+        <v>0.28673907980115088</v>
+      </c>
+      <c r="AT31" s="10">
+        <f>+AT12/AS12-1</f>
+        <v>0.35774000903392267</v>
+      </c>
+      <c r="AU31" s="10">
+        <f t="shared" ref="AU31:BD31" si="81">+AU12/AT12-1</f>
         <v>0.25</v>
       </c>
-      <c r="AT31" s="10">
-        <f t="shared" si="78"/>
+      <c r="AV31" s="10">
+        <f t="shared" si="81"/>
         <v>0.25</v>
       </c>
-      <c r="AU31" s="10">
-        <f t="shared" si="78"/>
-        <v>0.25000000000000022</v>
-      </c>
-      <c r="AV31" s="10">
-        <f t="shared" si="78"/>
+      <c r="AW31" s="10">
+        <f t="shared" si="81"/>
         <v>0.25</v>
       </c>
-      <c r="AW31" s="10">
-        <f t="shared" si="78"/>
+      <c r="AX31" s="10">
+        <f t="shared" si="81"/>
+        <v>0.25</v>
+      </c>
+      <c r="AY31" s="10">
+        <f t="shared" si="81"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AX31" s="10">
-        <f t="shared" si="78"/>
+      <c r="AZ31" s="10">
+        <f t="shared" si="81"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AY31" s="10">
-        <f t="shared" si="78"/>
+      <c r="BA31" s="10">
+        <f t="shared" si="81"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AZ31" s="10">
-        <f t="shared" si="78"/>
+      <c r="BB31" s="10">
+        <f t="shared" si="81"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="BA31" s="10">
-        <f t="shared" si="78"/>
+      <c r="BC31" s="10">
+        <f t="shared" si="81"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="BB31" s="10">
-        <f t="shared" si="78"/>
+      <c r="BD31" s="10">
+        <f t="shared" si="81"/>
         <v>0.10000000000000009</v>
       </c>
     </row>
-    <row r="32" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>71</v>
       </c>
       <c r="Q32" s="5">
-        <f t="shared" ref="Q32" si="79">Q8/M8-1</f>
+        <f t="shared" ref="Q32" si="82">Q8/M8-1</f>
         <v>0.10015631050760931</v>
       </c>
       <c r="R32" s="5">
         <f>R8/N8-1</f>
         <v>0.16787600828966021</v>
       </c>
-      <c r="AN32" s="10"/>
-      <c r="AO32" s="10"/>
-    </row>
-    <row r="33" spans="2:54" x14ac:dyDescent="0.25">
+      <c r="AP32" s="10"/>
+      <c r="AQ32" s="10"/>
+    </row>
+    <row r="33" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>85</v>
       </c>
       <c r="Q33" s="5"/>
       <c r="R33" s="5"/>
       <c r="T33" s="10">
-        <f>+T17/T12</f>
+        <f t="shared" ref="T33:AA33" si="83">+T17/T12</f>
         <v>0.18785105757931847</v>
       </c>
       <c r="U33" s="10">
-        <f>+U17/U12</f>
+        <f t="shared" si="83"/>
         <v>0.22427284517508497</v>
       </c>
       <c r="V33" s="10">
-        <f>+V17/V12</f>
+        <f t="shared" si="83"/>
         <v>0.17763444760173833</v>
       </c>
       <c r="W33" s="10">
-        <f>+W17/W12</f>
+        <f t="shared" si="83"/>
         <v>0.24097716211156861</v>
       </c>
       <c r="X33" s="10">
-        <f>+X17/X12</f>
+        <f t="shared" si="83"/>
         <v>0.29730186459968916</v>
       </c>
       <c r="Y33" s="10">
-        <f>+Y17/Y12</f>
+        <f t="shared" si="83"/>
         <v>0.25879560760996473</v>
       </c>
       <c r="Z33" s="10">
-        <f>+Z17/Z12</f>
+        <f t="shared" si="83"/>
         <v>0.26919103040631137</v>
       </c>
       <c r="AA33" s="10">
-        <f>+AA17/AA12</f>
+        <f t="shared" si="83"/>
         <v>0.27703734615395764</v>
       </c>
       <c r="AB33" s="10">
-        <f t="shared" ref="AB33:AD33" si="80">+AB17/AB12</f>
-        <v>1</v>
+        <f t="shared" ref="AB33:AE33" si="84">+AB17/AB12</f>
+        <v>0.24753834864626509</v>
       </c>
       <c r="AC33" s="10">
-        <f t="shared" si="80"/>
-        <v>1</v>
+        <f t="shared" si="84"/>
+        <v>0.2308645044371844</v>
       </c>
       <c r="AD33" s="10">
-        <f t="shared" si="80"/>
-        <v>1</v>
-      </c>
-      <c r="AN33" s="10">
-        <f t="shared" ref="AN33:BB33" si="81">+AN17/AN12</f>
+        <f t="shared" si="84"/>
+        <v>0.20741600301338273</v>
+      </c>
+      <c r="AE33" s="10">
+        <f t="shared" si="84"/>
+        <v>0.27808599167822468</v>
+      </c>
+      <c r="AP33" s="10">
+        <f t="shared" ref="AP33:BD33" si="85">+AP17/AP12</f>
         <v>0.18277744517062219</v>
       </c>
-      <c r="AO33" s="10">
-        <f t="shared" si="81"/>
+      <c r="AQ33" s="10">
+        <f t="shared" si="85"/>
         <v>0.16379752023772931</v>
       </c>
-      <c r="AP33" s="10">
-        <f t="shared" si="81"/>
+      <c r="AR33" s="10">
+        <f t="shared" si="85"/>
         <v>0.18971831609812137</v>
       </c>
-      <c r="AQ33" s="10">
-        <f t="shared" si="81"/>
+      <c r="AS33" s="10">
+        <f t="shared" si="85"/>
         <v>0.26723587228021028</v>
       </c>
-      <c r="AR33" s="10">
-        <f t="shared" si="81"/>
+      <c r="AT33" s="10">
+        <f t="shared" si="85"/>
         <v>0.35</v>
       </c>
-      <c r="AS33" s="10">
-        <f t="shared" si="81"/>
+      <c r="AU33" s="10">
+        <f t="shared" si="85"/>
         <v>0.4</v>
       </c>
-      <c r="AT33" s="10">
-        <f t="shared" si="81"/>
+      <c r="AV33" s="10">
+        <f t="shared" si="85"/>
         <v>0.45</v>
       </c>
-      <c r="AU33" s="10">
-        <f t="shared" si="81"/>
+      <c r="AW33" s="10">
+        <f t="shared" si="85"/>
         <v>0.5</v>
       </c>
-      <c r="AV33" s="10">
-        <f t="shared" si="81"/>
+      <c r="AX33" s="10">
+        <f t="shared" si="85"/>
         <v>0.55000000000000004</v>
       </c>
-      <c r="AW33" s="10">
-        <f t="shared" si="81"/>
+      <c r="AY33" s="10">
+        <f t="shared" si="85"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="AX33" s="10">
-        <f t="shared" si="81"/>
+      <c r="AZ33" s="10">
+        <f t="shared" si="85"/>
         <v>0.6</v>
       </c>
-      <c r="AY33" s="10">
-        <f t="shared" si="81"/>
+      <c r="BA33" s="10">
+        <f t="shared" si="85"/>
         <v>0.6</v>
       </c>
-      <c r="AZ33" s="10">
-        <f t="shared" si="81"/>
+      <c r="BB33" s="10">
+        <f t="shared" si="85"/>
         <v>0.6</v>
       </c>
-      <c r="BA33" s="10">
-        <f t="shared" si="81"/>
+      <c r="BC33" s="10">
+        <f t="shared" si="85"/>
         <v>0.6</v>
       </c>
-      <c r="BB33" s="10">
-        <f t="shared" si="81"/>
+      <c r="BD33" s="10">
+        <f t="shared" si="85"/>
         <v>0.6</v>
       </c>
     </row>
-    <row r="34" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="5">
-        <f t="shared" ref="G34:Q34" si="82">+G3/C3-1</f>
+        <f t="shared" ref="G34:Q34" si="86">+G3/C3-1</f>
         <v>0.49367088607594933</v>
       </c>
       <c r="H34" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>0.95321637426900563</v>
       </c>
       <c r="I34" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>0.96739130434782639</v>
       </c>
       <c r="J34" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>0.94240837696335067</v>
       </c>
       <c r="K34" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>0.78389830508474567</v>
       </c>
       <c r="L34" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>0.29341317365269481</v>
       </c>
       <c r="M34" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>0.30662983425414336</v>
       </c>
       <c r="N34" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>0.33423180592991919</v>
       </c>
       <c r="O34" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>0.28503562945368177</v>
       </c>
       <c r="P34" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>0.20833333333333326</v>
       </c>
       <c r="Q34" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>0.24312896405919671</v>
       </c>
       <c r="R34" s="5">
@@ -4514,24 +4673,24 @@
       <c r="S34" s="5"/>
       <c r="T34" s="5"/>
       <c r="U34" s="5"/>
-      <c r="AN34" s="10">
-        <f>AN3/AM3-1</f>
-        <v>0.33423180592991919</v>
-      </c>
-      <c r="AO34" s="10">
-        <f>AO3/AN3-1</f>
-        <v>0.18787878787878776</v>
-      </c>
       <c r="AP34" s="10">
         <f>AP3/AO3-1</f>
+        <v>0.33423180592991919</v>
+      </c>
+      <c r="AQ34" s="10">
+        <f>AQ3/AP3-1</f>
+        <v>0.18787878787878776</v>
+      </c>
+      <c r="AR34" s="10">
+        <f>AR3/AQ3-1</f>
         <v>-1</v>
       </c>
-      <c r="AQ34" s="10" t="e">
-        <f>AQ3/AP3-1</f>
+      <c r="AS34" s="10" t="e">
+        <f>AS3/AR3-1</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="36" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>65</v>
       </c>
@@ -4541,12 +4700,16 @@
       </c>
       <c r="W36" s="2"/>
       <c r="X36" s="2"/>
-      <c r="AO36" s="2">
-        <f>AO37-AO52</f>
+      <c r="AE36" s="2">
+        <f>+AE37-AE52</f>
+        <v>5157</v>
+      </c>
+      <c r="AQ36" s="2">
+        <f>AQ37-AQ52</f>
         <v>1988.4900000000002</v>
       </c>
     </row>
-    <row r="37" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>3</v>
       </c>
@@ -4558,11 +4721,15 @@
         <v>3469.4790000000003</v>
       </c>
       <c r="X37" s="2"/>
-      <c r="AO37" s="2">
+      <c r="AE37" s="2">
+        <f>1188+2011+2966</f>
+        <v>6165</v>
+      </c>
+      <c r="AQ37" s="2">
         <v>2977.4740000000002</v>
       </c>
     </row>
-    <row r="38" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>51</v>
       </c>
@@ -4573,11 +4740,14 @@
         <v>331.67700000000002</v>
       </c>
       <c r="X38" s="2"/>
-      <c r="AO38" s="2">
+      <c r="AE38" s="2">
+        <v>538</v>
+      </c>
+      <c r="AQ38" s="2">
         <v>379.35300000000001</v>
       </c>
     </row>
-    <row r="39" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>52</v>
       </c>
@@ -4588,11 +4758,14 @@
         <v>88.537000000000006</v>
       </c>
       <c r="X39" s="2"/>
-      <c r="AO39" s="2">
+      <c r="AE39" s="2">
+        <v>138</v>
+      </c>
+      <c r="AQ39" s="2">
         <v>61.640999999999998</v>
       </c>
     </row>
-    <row r="40" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>53</v>
       </c>
@@ -4605,12 +4778,16 @@
         <v>818.07900000000006</v>
       </c>
       <c r="X40" s="2"/>
-      <c r="AO40" s="2">
+      <c r="AE40" s="2">
+        <f>867+446</f>
+        <v>1313</v>
+      </c>
+      <c r="AQ40" s="2">
         <f>420.136+225.132</f>
         <v>645.26800000000003</v>
       </c>
     </row>
-    <row r="41" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>54</v>
       </c>
@@ -4621,11 +4798,14 @@
         <v>691.29200000000003</v>
       </c>
       <c r="X41" s="2"/>
-      <c r="AO41" s="2">
+      <c r="AE41" s="2">
+        <v>849</v>
+      </c>
+      <c r="AQ41" s="2">
         <v>592.346</v>
       </c>
     </row>
-    <row r="42" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>56</v>
       </c>
@@ -4636,11 +4816,14 @@
         <v>715.50099999999998</v>
       </c>
       <c r="X42" s="2"/>
-      <c r="AO42" s="2">
+      <c r="AE42" s="2">
+        <v>639</v>
+      </c>
+      <c r="AQ42" s="2">
         <v>526.03</v>
       </c>
     </row>
-    <row r="43" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>55</v>
       </c>
@@ -4653,12 +4836,16 @@
         <v>189.89400000000001</v>
       </c>
       <c r="X43" s="2"/>
-      <c r="AO43" s="2">
+      <c r="AE43" s="2">
+        <f>17+142</f>
+        <v>159</v>
+      </c>
+      <c r="AQ43" s="2">
         <f>54.717+134.335</f>
         <v>189.05200000000002</v>
       </c>
     </row>
-    <row r="44" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>57</v>
       </c>
@@ -4669,11 +4856,14 @@
         <v>10.212</v>
       </c>
       <c r="X44" s="2"/>
-      <c r="AO44" s="2">
+      <c r="AE44" s="2">
+        <v>26</v>
+      </c>
+      <c r="AQ44" s="2">
         <v>4.3230000000000004</v>
       </c>
     </row>
-    <row r="45" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>50</v>
       </c>
@@ -4682,52 +4872,68 @@
         <v>5375.4870000000001</v>
       </c>
       <c r="S45" s="2">
-        <f t="shared" ref="S45:AA45" si="83">SUM(S37:S44)</f>
+        <f t="shared" ref="S45:AE45" si="87">SUM(S37:S44)</f>
         <v>0</v>
       </c>
       <c r="T45" s="2">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="U45" s="2">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="V45" s="2">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="W45" s="2">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>6314.6710000000012</v>
       </c>
       <c r="X45" s="2">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="Y45" s="2">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="Z45" s="2">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AA45" s="2">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
-      <c r="AO45" s="2">
-        <f>SUM(AO37:AO44)</f>
+      <c r="AB45" s="2">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="AC45" s="2">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="AD45" s="2">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="AE45" s="2">
+        <f t="shared" si="87"/>
+        <v>9827</v>
+      </c>
+      <c r="AQ45" s="2">
+        <f>SUM(AQ37:AQ44)</f>
         <v>5375.4870000000001</v>
       </c>
     </row>
-    <row r="46" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:56" x14ac:dyDescent="0.25">
       <c r="R46"/>
       <c r="W46" s="2"/>
       <c r="X46" s="2"/>
     </row>
-    <row r="47" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>58</v>
       </c>
@@ -4738,11 +4944,14 @@
         <v>49.078000000000003</v>
       </c>
       <c r="X47" s="2"/>
-      <c r="AO47" s="2">
+      <c r="AE47" s="2">
+        <v>24</v>
+      </c>
+      <c r="AQ47" s="2">
         <v>71.182000000000002</v>
       </c>
     </row>
-    <row r="48" spans="2:54" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>59</v>
       </c>
@@ -4753,11 +4962,14 @@
         <v>273.649</v>
       </c>
       <c r="X48" s="2"/>
-      <c r="AO48" s="2">
+      <c r="AE48" s="2">
+        <v>435</v>
+      </c>
+      <c r="AQ48" s="2">
         <v>236.006</v>
       </c>
     </row>
-    <row r="49" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>36</v>
       </c>
@@ -4768,11 +4980,14 @@
         <v>292.67599999999999</v>
       </c>
       <c r="X49" s="2"/>
-      <c r="AO49" s="2">
+      <c r="AE49" s="2">
+        <v>424</v>
+      </c>
+      <c r="AQ49" s="2">
         <v>231.70400000000001</v>
       </c>
     </row>
-    <row r="50" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>60</v>
       </c>
@@ -4785,12 +5000,16 @@
         <v>3907.1459999999997</v>
       </c>
       <c r="X50" s="2"/>
-      <c r="AO50" s="2">
+      <c r="AE50" s="2">
+        <f>4425+2380</f>
+        <v>6805</v>
+      </c>
+      <c r="AQ50" s="2">
         <f>1941.943+1095.291</f>
         <v>3037.2339999999999</v>
       </c>
     </row>
-    <row r="51" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>61</v>
       </c>
@@ -4801,11 +5020,14 @@
         <v>693.81500000000005</v>
       </c>
       <c r="X51" s="2"/>
-      <c r="AO51" s="2">
+      <c r="AE51" s="2">
+        <v>625</v>
+      </c>
+      <c r="AQ51" s="2">
         <v>494.59</v>
       </c>
     </row>
-    <row r="52" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>4</v>
       </c>
@@ -4816,11 +5038,14 @@
         <v>1005.338</v>
       </c>
       <c r="X52" s="2"/>
-      <c r="AO52" s="2">
+      <c r="AE52" s="2">
+        <v>1008</v>
+      </c>
+      <c r="AQ52" s="2">
         <v>988.98400000000004</v>
       </c>
     </row>
-    <row r="53" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>62</v>
       </c>
@@ -4831,11 +5056,14 @@
         <v>30.282</v>
       </c>
       <c r="X53" s="2"/>
-      <c r="AO53" s="2">
+      <c r="AE53" s="2">
+        <v>95</v>
+      </c>
+      <c r="AQ53" s="2">
         <v>10.752000000000001</v>
       </c>
     </row>
-    <row r="54" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>63</v>
       </c>
@@ -4846,11 +5074,14 @@
         <v>62.686999999999998</v>
       </c>
       <c r="X54" s="2"/>
-      <c r="AO54" s="2">
+      <c r="AE54" s="2">
+        <v>411</v>
+      </c>
+      <c r="AQ54" s="2">
         <v>305.03500000000003</v>
       </c>
     </row>
-    <row r="55" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>64</v>
       </c>
@@ -4870,17 +5101,21 @@
         <f>SUM(Y47:Y54)</f>
         <v>0</v>
       </c>
-      <c r="AO55" s="2">
-        <f>SUM(AO47:AO54)</f>
+      <c r="AE55" s="2">
+        <f>SUM(AE47:AE54)</f>
+        <v>9827</v>
+      </c>
+      <c r="AQ55" s="2">
+        <f>SUM(AQ47:AQ54)</f>
         <v>5375.487000000001</v>
       </c>
     </row>
-    <row r="56" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:43" x14ac:dyDescent="0.25">
       <c r="R56"/>
       <c r="W56" s="2"/>
       <c r="X56" s="2"/>
     </row>
-    <row r="57" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>77</v>
       </c>
@@ -4888,22 +5123,22 @@
       <c r="W57" s="2"/>
       <c r="X57" s="2"/>
     </row>
-    <row r="58" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:43" x14ac:dyDescent="0.25">
       <c r="R58"/>
       <c r="W58" s="2"/>
       <c r="X58" s="2"/>
     </row>
-    <row r="59" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:43" x14ac:dyDescent="0.25">
       <c r="R59"/>
       <c r="W59" s="2"/>
       <c r="X59" s="2"/>
     </row>
-    <row r="60" spans="2:41" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:43" x14ac:dyDescent="0.25">
       <c r="R60"/>
       <c r="W60" s="2"/>
       <c r="X60" s="2"/>
     </row>
-    <row r="61" spans="2:41" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:43" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B61" s="2" t="s">
         <v>66</v>
       </c>
@@ -4964,17 +5199,29 @@
       <c r="AA61" s="2">
         <v>443.91399999999999</v>
       </c>
-      <c r="AM61" s="2">
+      <c r="AB61" s="2">
+        <v>199.262</v>
+      </c>
+      <c r="AC61" s="2">
+        <v>546.18399999999997</v>
+      </c>
+      <c r="AD61" s="2">
+        <v>606.99800000000005</v>
+      </c>
+      <c r="AE61" s="2">
+        <v>629</v>
+      </c>
+      <c r="AO61" s="2">
         <v>524.34</v>
       </c>
-      <c r="AN61" s="2">
+      <c r="AP61" s="2">
         <v>659.10900000000004</v>
       </c>
-      <c r="AO61" s="2">
+      <c r="AQ61" s="2">
         <v>369.29599999999999</v>
       </c>
     </row>
-    <row r="62" spans="2:41" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:43" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="s">
         <v>78</v>
       </c>
@@ -5035,8 +5282,20 @@
       <c r="AA62" s="2">
         <v>17.364999999999998</v>
       </c>
-    </row>
-    <row r="63" spans="2:41" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AB62" s="2">
+        <v>22.61</v>
+      </c>
+      <c r="AC62" s="2">
+        <v>102.5582</v>
+      </c>
+      <c r="AD62" s="2">
+        <v>298.42099999999999</v>
+      </c>
+      <c r="AE62" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="63" spans="2:43" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="2" t="s">
         <v>79</v>
       </c>
@@ -5050,104 +5309,135 @@
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
       <c r="L63" s="7">
-        <f t="shared" ref="L63:N63" si="84">+L61-L62</f>
+        <f t="shared" ref="L63:N63" si="88">+L61-L62</f>
         <v>168.01600000000002</v>
       </c>
       <c r="M63" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>178.203</v>
       </c>
       <c r="N63" s="7">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>0</v>
       </c>
       <c r="O63" s="7">
-        <f>+O61-O62</f>
+        <f t="shared" ref="O63:AD63" si="89">+O61-O62</f>
         <v>104.64600000000002</v>
       </c>
       <c r="P63" s="7">
-        <f>+P61-P62</f>
+        <f t="shared" si="89"/>
         <v>-57.314999999999998</v>
       </c>
       <c r="Q63" s="7">
-        <f>+Q61-Q62</f>
+        <f t="shared" si="89"/>
         <v>-66.211999999999989</v>
       </c>
       <c r="R63" s="7">
-        <f>+R61-R62</f>
+        <f t="shared" si="89"/>
         <v>-37.986000000000018</v>
       </c>
       <c r="S63" s="7">
-        <f>+S61-S62</f>
+        <f t="shared" si="89"/>
         <v>82.422000000000011</v>
       </c>
       <c r="T63" s="7">
-        <f>+T61-T62</f>
+        <f t="shared" si="89"/>
         <v>-82.525000000000006</v>
       </c>
       <c r="U63" s="7">
-        <f>+U61-U62</f>
+        <f t="shared" si="89"/>
         <v>59.507999999999996</v>
       </c>
       <c r="V63" s="7">
-        <f>+V61-V62</f>
+        <f t="shared" si="89"/>
         <v>78.108000000000004</v>
       </c>
       <c r="W63" s="2">
-        <f>+W61-W62</f>
+        <f t="shared" si="89"/>
         <v>192.26599999999999</v>
       </c>
       <c r="X63" s="2">
-        <f>+X61-X62</f>
+        <f t="shared" si="89"/>
         <v>111.74799999999999</v>
       </c>
       <c r="Y63" s="2">
-        <f>+Y61-Y62</f>
+        <f t="shared" si="89"/>
         <v>218.02500000000009</v>
       </c>
       <c r="Z63" s="2">
-        <f>+Z61-Z62</f>
+        <f t="shared" si="89"/>
         <v>120.63100000000001</v>
       </c>
       <c r="AA63" s="2">
-        <f>+AA61-AA62</f>
+        <f t="shared" si="89"/>
         <v>426.54899999999998</v>
       </c>
-    </row>
-    <row r="64" spans="2:41" x14ac:dyDescent="0.25">
+      <c r="AB63" s="2">
+        <f t="shared" si="89"/>
+        <v>176.65199999999999</v>
+      </c>
+      <c r="AC63" s="2">
+        <f t="shared" si="89"/>
+        <v>443.62579999999997</v>
+      </c>
+      <c r="AD63" s="2">
+        <f t="shared" si="89"/>
+        <v>308.57700000000006</v>
+      </c>
+      <c r="AE63" s="2">
+        <f>+AE61-AE62</f>
+        <v>596</v>
+      </c>
+    </row>
+    <row r="64" spans="2:43" x14ac:dyDescent="0.25">
       <c r="T64" s="2">
-        <f>SUM(Q63:T63)</f>
+        <f t="shared" ref="T64:AA64" si="90">SUM(Q63:T63)</f>
         <v>-104.301</v>
       </c>
       <c r="U64" s="2">
-        <f>SUM(R63:U63)</f>
+        <f t="shared" si="90"/>
         <v>21.418999999999983</v>
       </c>
       <c r="V64" s="2">
-        <f>SUM(S63:V63)</f>
+        <f t="shared" si="90"/>
         <v>137.51300000000001</v>
       </c>
       <c r="W64" s="2">
-        <f>SUM(T63:W63)</f>
+        <f t="shared" si="90"/>
         <v>247.35699999999997</v>
       </c>
       <c r="X64" s="2">
-        <f>SUM(U63:X63)</f>
+        <f t="shared" si="90"/>
         <v>441.62999999999994</v>
       </c>
       <c r="Y64" s="2">
-        <f>SUM(V63:Y63)</f>
+        <f t="shared" si="90"/>
         <v>600.14700000000016</v>
       </c>
       <c r="Z64" s="2">
-        <f>SUM(W63:Z63)</f>
+        <f t="shared" si="90"/>
         <v>642.67000000000007</v>
       </c>
       <c r="AA64" s="2">
         <f>SUM(X63:AA63)</f>
         <v>876.95300000000009</v>
       </c>
-      <c r="AB64" s="2"/>
+      <c r="AB64" s="2">
+        <f>SUM(Y63:AB63)</f>
+        <v>941.8570000000002</v>
+      </c>
+      <c r="AC64" s="2">
+        <f>SUM(Z63:AC63)</f>
+        <v>1167.4577999999999</v>
+      </c>
+      <c r="AD64" s="2">
+        <f>SUM(AA63:AD63)</f>
+        <v>1355.4038</v>
+      </c>
+      <c r="AE64" s="2">
+        <f>SUM(AB63:AE63)</f>
+        <v>1524.8548000000001</v>
+      </c>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
